--- a/product-definitions/spreadsheet/nox-noxy-concentration.xlsx
+++ b/product-definitions/spreadsheet/nox-noxy-concentration.xlsx
@@ -272,7 +272,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -306,11 +306,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -401,7 +396,7 @@
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
